--- a/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/fare_rules.xlsx
+++ b/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/fare_rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\fatecsp-MA20262-equipe-07-colossenses\MA2026-projeto-pratico\MA2026-entrega-parcial\01-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1FBE14DC-BE7A-469B-85D4-ED351E86826D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9A5A95-8C47-437B-973A-72921A5BB189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{91AB4F98-BB36-4922-B0E8-BEF2A9FE0E6F}"/>
   </bookViews>
@@ -4686,7 +4686,26 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4697,6 +4716,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CDD96BFB-EF5D-413F-84E9-260B5711D94E}" name="Fare_rules" displayName="Fare_rules" ref="A1:E5445" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:E5445" xr:uid="{CDD96BFB-EF5D-413F-84E9-260B5711D94E}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9041907E-CC4D-4691-A86E-932D71AA7926}" name="fare_id"/>
+    <tableColumn id="2" xr3:uid="{18A0A7AD-AAB4-4199-AA2B-61C3E4AE8B37}" name="route_id"/>
+    <tableColumn id="3" xr3:uid="{23D4B347-F807-43B1-AD2C-B26E45A12DB9}" name="origin_id"/>
+    <tableColumn id="4" xr3:uid="{24DE34D2-4743-452F-8C02-EF1BB790C8FE}" name="destination_id"/>
+    <tableColumn id="5" xr3:uid="{56044331-4111-49E8-B0D0-F73B90F03451}" name="contains_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5021,7 +5054,9 @@
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -48598,5 +48633,8 @@
     <sortCondition ref="B4081:B5445"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>